--- a/franquias/pwr_reports/KEYS Service Main Service Exceptions - Franquias (Stores)(2026-08-31 - 2026-09-06).xlsx
+++ b/franquias/pwr_reports/KEYS Service Main Service Exceptions - Franquias (Stores)(2026-08-31 - 2026-09-06).xlsx
@@ -875,19 +875,19 @@
     <t>174</t>
   </si>
   <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>R$ 43.693,19</t>
-  </si>
-  <si>
-    <t>439.5</t>
-  </si>
-  <si>
-    <t>278.5</t>
-  </si>
-  <si>
-    <t>6.23</t>
+    <t>152</t>
+  </si>
+  <si>
+    <t>R$ 44.205,22</t>
+  </si>
+  <si>
+    <t>457.8</t>
+  </si>
+  <si>
+    <t>289.9</t>
+  </si>
+  <si>
+    <t>6.27</t>
   </si>
   <si>
     <t>21.8</t>
@@ -899,19 +899,19 @@
     <t>6.5</t>
   </si>
   <si>
-    <t>30.6%</t>
-  </si>
-  <si>
-    <t>17.8%</t>
+    <t>30.2%</t>
+  </si>
+  <si>
+    <t>17.9%</t>
   </si>
   <si>
     <t>2.0%</t>
   </si>
   <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>4.6%</t>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>4.5%</t>
   </si>
   <si>
     <t>1.5%</t>
@@ -923,46 +923,46 @@
     <t>6.2%</t>
   </si>
   <si>
-    <t>2.3%</t>
-  </si>
-  <si>
-    <t>4.8%</t>
-  </si>
-  <si>
-    <t>9609.0</t>
-  </si>
-  <si>
-    <t>7752.0</t>
-  </si>
-  <si>
-    <t>852.0</t>
-  </si>
-  <si>
-    <t>279.0</t>
-  </si>
-  <si>
-    <t>2007.0</t>
-  </si>
-  <si>
-    <t>650.0</t>
-  </si>
-  <si>
-    <t>76.0</t>
-  </si>
-  <si>
-    <t>2703.0</t>
-  </si>
-  <si>
-    <t>1010.0</t>
-  </si>
-  <si>
-    <t>2083.0</t>
+    <t>2.4%</t>
+  </si>
+  <si>
+    <t>4.9%</t>
+  </si>
+  <si>
+    <t>10029.0</t>
+  </si>
+  <si>
+    <t>8116.0</t>
+  </si>
+  <si>
+    <t>882.0</t>
+  </si>
+  <si>
+    <t>294.0</t>
+  </si>
+  <si>
+    <t>2053.0</t>
+  </si>
+  <si>
+    <t>671.0</t>
+  </si>
+  <si>
+    <t>83.0</t>
+  </si>
+  <si>
+    <t>2824.0</t>
+  </si>
+  <si>
+    <t>1074.0</t>
+  </si>
+  <si>
+    <t>2206.0</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>228.0</t>
+    <t>236.0</t>
   </si>
   <si>
     <t>1</t>
@@ -3737,7 +3737,7 @@
         <v>19546</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C16" s="4">
         <v>51</v>
@@ -3768,40 +3768,40 @@
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="5">
-        <v>46100.670000000006</v>
+        <v>45298.690000000002</v>
       </c>
       <c r="N16" s="6">
-        <v>417</v>
+        <v>484</v>
       </c>
       <c r="O16" s="6">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="P16" s="7">
-        <v>3.1423324455205814</v>
+        <v>3.0726041666666664</v>
       </c>
       <c r="Q16" s="8">
-        <v>20.07330277777778</v>
+        <v>19.698155731225295</v>
       </c>
       <c r="R16" s="8">
-        <v>10.0102625</v>
+        <v>9.7142198412698413</v>
       </c>
       <c r="S16" s="8">
         <v>7</v>
       </c>
       <c r="T16" s="9">
-        <v>0.30092592592592593</v>
+        <v>0.33596837944664032</v>
       </c>
       <c r="U16" s="9">
-        <v>0.18433179723502305</v>
+        <v>0.17322834645669291</v>
       </c>
       <c r="V16" s="9">
-        <v>0.004608294930875576</v>
+        <v>0.003937007874015748</v>
       </c>
       <c r="W16" s="9">
         <v>0</v>
       </c>
       <c r="X16" s="9">
-        <v>0.10138248847926268</v>
+        <v>0.094488188976377951</v>
       </c>
       <c r="Y16" s="9">
         <v>0</v>
@@ -3810,19 +3810,19 @@
         <v>0</v>
       </c>
       <c r="AA16" s="9">
-        <v>0.0092165898617511521</v>
+        <v>0.011811023622047244</v>
       </c>
       <c r="AB16" s="9">
-        <v>0.0092165898617511521</v>
+        <v>0.011811023622047244</v>
       </c>
       <c r="AC16" s="9">
-        <v>0.073732718894009217</v>
+        <v>0.062992125984251968</v>
       </c>
       <c r="AD16" s="6">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AE16" s="6">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AF16" s="6">
         <v>1</v>
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="AH16" s="6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI16" s="6">
         <v>0</v>
@@ -3840,10 +3840,10 @@
         <v>0</v>
       </c>
       <c r="AK16" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL16" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM16" s="6">
         <v>16</v>
@@ -3894,7 +3894,7 @@
         <v>19547</v>
       </c>
       <c r="B17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C17" s="4">
         <v>51</v>
@@ -3925,61 +3925,61 @@
       </c>
       <c r="L17" s="4"/>
       <c r="M17" s="5">
-        <v>36085.594999999994</v>
+        <v>37020.869999999995</v>
       </c>
       <c r="N17" s="6">
-        <v>344</v>
+        <v>411</v>
       </c>
       <c r="O17" s="6">
-        <v>189</v>
+        <v>230</v>
       </c>
       <c r="P17" s="7">
-        <v>9.3126684971098275</v>
+        <v>8.9311243373493969</v>
       </c>
       <c r="Q17" s="8">
-        <v>27.737234042553194</v>
+        <v>26.816084279475984</v>
       </c>
       <c r="R17" s="8">
-        <v>10.687362087912087</v>
+        <v>10.025784304932735</v>
       </c>
       <c r="S17" s="8">
         <v>8</v>
       </c>
       <c r="T17" s="9">
-        <v>0.063829787234042548</v>
+        <v>0.074235807860262015</v>
       </c>
       <c r="U17" s="9">
-        <v>0.14285714285714285</v>
+        <v>0.17826086956521739</v>
       </c>
       <c r="V17" s="9">
-        <v>0.026455026455026454</v>
+        <v>0.021739130434782608</v>
       </c>
       <c r="W17" s="9">
         <v>0</v>
       </c>
       <c r="X17" s="9">
-        <v>0.0052910052910052907</v>
+        <v>0.0043478260869565218</v>
       </c>
       <c r="Y17" s="9">
         <v>0</v>
       </c>
       <c r="Z17" s="9">
-        <v>0.010582010582010581</v>
+        <v>0.017391304347826087</v>
       </c>
       <c r="AA17" s="9">
-        <v>0.037037037037037035</v>
+        <v>0.034782608695652174</v>
       </c>
       <c r="AB17" s="9">
-        <v>0.052910052910052907</v>
+        <v>0.052173913043478258</v>
       </c>
       <c r="AC17" s="9">
-        <v>0.021164021164021163</v>
+        <v>0.060869565217391307</v>
       </c>
       <c r="AD17" s="6">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AE17" s="6">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="AF17" s="6">
         <v>5</v>
@@ -3994,16 +3994,16 @@
         <v>0</v>
       </c>
       <c r="AJ17" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AK17" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL17" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AM17" s="6">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AN17" s="9">
         <v>0</v>
@@ -4522,7 +4522,7 @@
         <v>19553</v>
       </c>
       <c r="B21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C21" s="4">
         <v>51</v>
@@ -4551,49 +4551,49 @@
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="5">
-        <v>49856.100000000006</v>
+        <v>55585.120000000003</v>
       </c>
       <c r="N21" s="6">
-        <v>384</v>
+        <v>508</v>
       </c>
       <c r="O21" s="6">
-        <v>266</v>
+        <v>335</v>
       </c>
       <c r="P21" s="7">
-        <v>7.727750125944584</v>
+        <v>6.546264559386973</v>
       </c>
       <c r="Q21" s="8">
-        <v>24.287845112781952</v>
+        <v>22.792637313432834</v>
       </c>
       <c r="R21" s="8">
-        <v>9.8648359848484848</v>
+        <v>9.4321212121212117</v>
       </c>
       <c r="S21" s="8">
         <v>7</v>
       </c>
       <c r="T21" s="9">
-        <v>0.28947368421052633</v>
+        <v>0.29253731343283584</v>
       </c>
       <c r="U21" s="9">
-        <v>0.14285714285714285</v>
+        <v>0.15223880597014924</v>
       </c>
       <c r="V21" s="9">
-        <v>0.0075187969924812026</v>
+        <v>0.011940298507462687</v>
       </c>
       <c r="W21" s="9">
         <v>0</v>
       </c>
       <c r="X21" s="9">
-        <v>0.018796992481203006</v>
+        <v>0.026865671641791045</v>
       </c>
       <c r="Y21" s="9">
-        <v>0</v>
+        <v>0.0029850746268656717</v>
       </c>
       <c r="Z21" s="9">
-        <v>0.0075187969924812026</v>
+        <v>0.0059701492537313433</v>
       </c>
       <c r="AA21" s="9">
-        <v>0.0075187969924812026</v>
+        <v>0.017910447761194031</v>
       </c>
       <c r="AB21" s="9">
         <v>0</v>
@@ -4602,28 +4602,28 @@
         <v>0</v>
       </c>
       <c r="AD21" s="6">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="AE21" s="6">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="AF21" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG21" s="6">
         <v>0</v>
       </c>
       <c r="AH21" s="6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AI21" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ21" s="6">
         <v>2</v>
       </c>
       <c r="AK21" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AL21" s="6">
         <v>0</v>
@@ -4632,10 +4632,10 @@
         <v>0</v>
       </c>
       <c r="AN21" s="9">
-        <v>0.10526315789473684</v>
+        <v>0.10149253731343283</v>
       </c>
       <c r="AO21" s="6">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c t="s" r="AP21" s="4">
         <v>58</v>
@@ -4991,7 +4991,7 @@
         <v>19565</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -5022,61 +5022,61 @@
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="5">
-        <v>46682.46333333334</v>
+        <v>52412.449999999997</v>
       </c>
       <c r="N24" s="6">
-        <v>452</v>
+        <v>592</v>
       </c>
       <c r="O24" s="6">
-        <v>259</v>
+        <v>342</v>
       </c>
       <c r="P24" s="7">
-        <v>2.728625512528474</v>
+        <v>2.7664343205574911</v>
       </c>
       <c r="Q24" s="8">
-        <v>15.419369884169884</v>
+        <v>15.196491520467836</v>
       </c>
       <c r="R24" s="8">
-        <v>6.0784757847533628</v>
+        <v>5.4333884868421052</v>
       </c>
       <c r="S24" s="8">
         <v>8</v>
       </c>
       <c r="T24" s="9">
-        <v>0.5714285714285714</v>
+        <v>0.60233918128654973</v>
       </c>
       <c r="U24" s="9">
-        <v>0.29343629343629346</v>
+        <v>0.26608187134502925</v>
       </c>
       <c r="V24" s="9">
-        <v>0.038610038610038609</v>
+        <v>0.029239766081871343</v>
       </c>
       <c r="W24" s="9">
-        <v>0.0077220077220000001</v>
+        <v>0.0058479532160000004</v>
       </c>
       <c r="X24" s="9">
-        <v>0.069498069498069498</v>
+        <v>0.070175438596491224</v>
       </c>
       <c r="Y24" s="9">
-        <v>0.034749034749034749</v>
+        <v>0.026315789473684209</v>
       </c>
       <c r="Z24" s="9">
-        <v>0.0038610038610038611</v>
+        <v>0.0058479532163742687</v>
       </c>
       <c r="AA24" s="9">
-        <v>0.19305019305019305</v>
+        <v>0.16959064327485379</v>
       </c>
       <c r="AB24" s="9">
-        <v>0.042471042471042469</v>
+        <v>0.040935672514619881</v>
       </c>
       <c r="AC24" s="9">
         <v>0</v>
       </c>
       <c r="AD24" s="6">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="AE24" s="6">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="AF24" s="6">
         <v>10</v>
@@ -5085,19 +5085,19 @@
         <v>2</v>
       </c>
       <c r="AH24" s="6">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AI24" s="6">
         <v>9</v>
       </c>
       <c r="AJ24" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK24" s="6">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="AL24" s="6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AM24" s="6">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>19579</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>51</v>
@@ -5493,61 +5493,61 @@
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="5">
-        <v>32873.715000000004</v>
+        <v>34614.949999999997</v>
       </c>
       <c r="N27" s="6">
-        <v>337</v>
+        <v>403</v>
       </c>
       <c r="O27" s="6">
-        <v>251</v>
+        <v>303</v>
       </c>
       <c r="P27" s="7">
-        <v>6.2348097142857144</v>
+        <v>6.6806492788461531</v>
       </c>
       <c r="Q27" s="8">
-        <v>23.838999999999999</v>
+        <v>23.517549668874175</v>
       </c>
       <c r="R27" s="8">
-        <v>10.696448360655737</v>
+        <v>9.7430182432432435</v>
       </c>
       <c r="S27" s="8">
         <v>7</v>
       </c>
       <c r="T27" s="9">
-        <v>0.20000000000000001</v>
+        <v>0.17549668874172186</v>
       </c>
       <c r="U27" s="9">
-        <v>0.13147410358565736</v>
+        <v>0.11221122112211221</v>
       </c>
       <c r="V27" s="9">
-        <v>0.023904382470119521</v>
+        <v>0.019801980198019802</v>
       </c>
       <c r="W27" s="9">
-        <v>0.0039840637450000004</v>
+        <v>0.0033003300330000001</v>
       </c>
       <c r="X27" s="9">
-        <v>0.035856573705179286</v>
+        <v>0.029702970297029702</v>
       </c>
       <c r="Y27" s="9">
-        <v>0.015936254980079681</v>
+        <v>0.013201320132013201</v>
       </c>
       <c r="Z27" s="9">
-        <v>0.0039840637450199202</v>
+        <v>0.0033003300330033004</v>
       </c>
       <c r="AA27" s="9">
-        <v>0.031872509960159362</v>
+        <v>0.026402640264026403</v>
       </c>
       <c r="AB27" s="9">
-        <v>0.011952191235059761</v>
+        <v>0.013201320132013201</v>
       </c>
       <c r="AC27" s="9">
-        <v>0.039840637450199202</v>
+        <v>0.033003300330033</v>
       </c>
       <c r="AD27" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AE27" s="6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AF27" s="6">
         <v>6</v>
@@ -5568,7 +5568,7 @@
         <v>8</v>
       </c>
       <c r="AL27" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM27" s="6">
         <v>10</v>
@@ -5776,7 +5776,7 @@
         <v>19581</v>
       </c>
       <c r="B29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C29" s="4">
         <v>51</v>
@@ -5807,67 +5807,67 @@
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="5">
-        <v>44986.421666666662</v>
+        <v>56445.789999999994</v>
       </c>
       <c r="N29" s="6">
-        <v>381</v>
+        <v>555</v>
       </c>
       <c r="O29" s="6">
-        <v>305</v>
+        <v>440</v>
       </c>
       <c r="P29" s="7">
-        <v>4.192057291666667</v>
+        <v>7.4566967567567568</v>
       </c>
       <c r="Q29" s="8">
-        <v>31.145434653465344</v>
+        <v>34.100343249427915</v>
       </c>
       <c r="R29" s="8">
-        <v>19.547627118644069</v>
+        <v>19.398352941176469</v>
       </c>
       <c r="S29" s="8">
         <v>8</v>
       </c>
       <c r="T29" s="9">
-        <v>0.10231023102310231</v>
+        <v>0.07780320366132723</v>
       </c>
       <c r="U29" s="9">
-        <v>0.14754098360655737</v>
+        <v>0.16363636363636364</v>
       </c>
       <c r="V29" s="9">
-        <v>0.019672131147540985</v>
+        <v>0.013636363636363636</v>
       </c>
       <c r="W29" s="9">
-        <v>0.0032786885240000002</v>
+        <v>0.004545454545</v>
       </c>
       <c r="X29" s="9">
-        <v>0.026229508196721311</v>
+        <v>0.018181818181818181</v>
       </c>
       <c r="Y29" s="9">
-        <v>0.0098360655737704927</v>
+        <v>0.0068181818181818179</v>
       </c>
       <c r="Z29" s="9">
         <v>0</v>
       </c>
       <c r="AA29" s="9">
-        <v>0.045901639344262293</v>
+        <v>0.040909090909090909</v>
       </c>
       <c r="AB29" s="9">
-        <v>0.0098360655737704927</v>
+        <v>0.0068181818181818179</v>
       </c>
       <c r="AC29" s="9">
-        <v>0.059016393442622953</v>
+        <v>0.090909090909090912</v>
       </c>
       <c r="AD29" s="6">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="AE29" s="6">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="AF29" s="6">
         <v>6</v>
       </c>
       <c r="AG29" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH29" s="6">
         <v>8</v>
@@ -5879,13 +5879,13 @@
         <v>0</v>
       </c>
       <c r="AK29" s="6">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AL29" s="6">
         <v>3</v>
       </c>
       <c r="AM29" s="6">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="AN29" s="9">
         <v>0</v>
@@ -6090,7 +6090,7 @@
         <v>19596</v>
       </c>
       <c r="B31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C31" s="4">
         <v>51</v>
@@ -6119,64 +6119,64 @@
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="5">
-        <v>42680.458333333336</v>
+        <v>49375.029999999992</v>
       </c>
       <c r="N31" s="6">
-        <v>422</v>
+        <v>556</v>
       </c>
       <c r="O31" s="6">
-        <v>234</v>
+        <v>315</v>
       </c>
       <c r="P31" s="7">
-        <v>5.234684520884521</v>
+        <v>6.3666972375690607</v>
       </c>
       <c r="Q31" s="8">
-        <v>22.78075793991416</v>
+        <v>24.810774840764331</v>
       </c>
       <c r="R31" s="8">
-        <v>9.6308589519650649</v>
+        <v>9.9670983818770225</v>
       </c>
       <c r="S31" s="8">
         <v>7</v>
       </c>
       <c r="T31" s="9">
-        <v>0.23605150214592274</v>
+        <v>0.19426751592356689</v>
       </c>
       <c r="U31" s="9">
-        <v>0.14529914529914531</v>
+        <v>0.12698412698412698</v>
       </c>
       <c r="V31" s="9">
-        <v>0.038461538461538464</v>
+        <v>0.031746031746031744</v>
       </c>
       <c r="W31" s="9">
-        <v>0.0042735042730000002</v>
+        <v>0.003174603174</v>
       </c>
       <c r="X31" s="9">
-        <v>0.072649572649572655</v>
+        <v>0.053968253968253971</v>
       </c>
       <c r="Y31" s="9">
-        <v>0.017094017094017096</v>
+        <v>0.015873015873015872</v>
       </c>
       <c r="Z31" s="9">
         <v>0</v>
       </c>
       <c r="AA31" s="9">
-        <v>0.017094017094017096</v>
+        <v>0.015873015873015872</v>
       </c>
       <c r="AB31" s="9">
-        <v>0.038461538461538464</v>
+        <v>0.041269841269841269</v>
       </c>
       <c r="AC31" s="9">
-        <v>0.0085470085470085479</v>
+        <v>0.0063492063492063492</v>
       </c>
       <c r="AD31" s="6">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="AE31" s="6">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AF31" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG31" s="6">
         <v>1</v>
@@ -6185,16 +6185,16 @@
         <v>17</v>
       </c>
       <c r="AI31" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ31" s="6">
         <v>0</v>
       </c>
       <c r="AK31" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL31" s="6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AM31" s="6">
         <v>2</v>
@@ -6712,7 +6712,7 @@
         <v>19601</v>
       </c>
       <c r="B35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C35" s="4">
         <v>51</v>
@@ -6743,85 +6743,85 @@
       </c>
       <c r="L35" s="4"/>
       <c r="M35" s="5">
-        <v>39294.640000000007</v>
+        <v>44699.560000000005</v>
       </c>
       <c r="N35" s="6">
-        <v>391</v>
+        <v>514</v>
       </c>
       <c r="O35" s="6">
-        <v>251</v>
+        <v>326</v>
       </c>
       <c r="P35" s="7">
-        <v>2.7795252688172045</v>
+        <v>2.9444557809330631</v>
       </c>
       <c r="Q35" s="8">
-        <v>15.925763745019921</v>
+        <v>15.970807975460122</v>
       </c>
       <c r="R35" s="8">
-        <v>5.3808745901639341</v>
+        <v>5.3978770700636938</v>
       </c>
       <c r="S35" s="8">
         <v>8</v>
       </c>
       <c r="T35" s="9">
-        <v>0.51792828685258963</v>
+        <v>0.49079754601226994</v>
       </c>
       <c r="U35" s="9">
-        <v>0.24701195219123506</v>
+        <v>0.26993865030674846</v>
       </c>
       <c r="V35" s="9">
-        <v>0.023904382470119521</v>
+        <v>0.021472392638036811</v>
       </c>
       <c r="W35" s="9">
         <v>0</v>
       </c>
       <c r="X35" s="9">
-        <v>0.059760956175298807</v>
+        <v>0.052147239263803678</v>
       </c>
       <c r="Y35" s="9">
-        <v>0.0039840637450199202</v>
+        <v>0.012269938650306749</v>
       </c>
       <c r="Z35" s="9">
         <v>0</v>
       </c>
       <c r="AA35" s="9">
-        <v>0.087649402390438252</v>
+        <v>0.10122699386503067</v>
       </c>
       <c r="AB35" s="9">
-        <v>0.079681274900398405</v>
+        <v>0.095092024539877307</v>
       </c>
       <c r="AC35" s="9">
-        <v>0.0079681274900398405</v>
+        <v>0.012269938650306749</v>
       </c>
       <c r="AD35" s="6">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="AE35" s="6">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="AF35" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG35" s="6">
         <v>0</v>
       </c>
       <c r="AH35" s="6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI35" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ35" s="6">
         <v>0</v>
       </c>
       <c r="AK35" s="6">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="AL35" s="6">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="AM35" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN35" s="9">
         <v>0</v>
@@ -7280,7 +7280,7 @@
         <v>19609</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>51</v>
@@ -7311,70 +7311,70 @@
       </c>
       <c r="L39" s="4"/>
       <c r="M39" s="5">
-        <v>35126.489999999998</v>
+        <v>38970.830000000002</v>
       </c>
       <c r="N39" s="6">
-        <v>322</v>
+        <v>420</v>
       </c>
       <c r="O39" s="6">
-        <v>262</v>
+        <v>328</v>
       </c>
       <c r="P39" s="7">
-        <v>5.8586914110429449</v>
+        <v>5.7410560283687939</v>
       </c>
       <c r="Q39" s="8">
-        <v>28.698791221374048</v>
+        <v>27.85685975609756</v>
       </c>
       <c r="R39" s="8">
-        <v>15.729566283524903</v>
+        <v>14.955351987767584</v>
       </c>
       <c r="S39" s="8">
         <v>7</v>
       </c>
       <c r="T39" s="9">
-        <v>0.13740458015267176</v>
+        <v>0.14634146341463414</v>
       </c>
       <c r="U39" s="9">
-        <v>0.072519083969465645</v>
+        <v>0.088414634146341459</v>
       </c>
       <c r="V39" s="9">
-        <v>0.011450381679389313</v>
+        <v>0.012195121951219513</v>
       </c>
       <c r="W39" s="9">
         <v>0</v>
       </c>
       <c r="X39" s="9">
-        <v>0.0076335877862595417</v>
+        <v>0.012195121951219513</v>
       </c>
       <c r="Y39" s="9">
-        <v>0.0038167938931297708</v>
+        <v>0.0030487804878048782</v>
       </c>
       <c r="Z39" s="9">
         <v>0</v>
       </c>
       <c r="AA39" s="9">
-        <v>0.011450381679389313</v>
+        <v>0.0091463414634146336</v>
       </c>
       <c r="AB39" s="9">
-        <v>0.0038167938931297708</v>
+        <v>0.0030487804878048782</v>
       </c>
       <c r="AC39" s="9">
-        <v>0.030534351145038167</v>
+        <v>0.042682926829268296</v>
       </c>
       <c r="AD39" s="6">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AE39" s="6">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="AF39" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG39" s="6">
         <v>0</v>
       </c>
       <c r="AH39" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI39" s="6">
         <v>1</v>
@@ -7389,13 +7389,13 @@
         <v>1</v>
       </c>
       <c r="AM39" s="6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AN39" s="9">
-        <v>0.0076335877862595417</v>
+        <v>0.0091463414634146336</v>
       </c>
       <c r="AO39" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c t="s" r="AP39" s="4">
         <v>58</v>
@@ -8005,7 +8005,7 @@
         <v>19622</v>
       </c>
       <c r="B44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C44" s="4">
         <v>51</v>
@@ -8036,31 +8036,31 @@
       </c>
       <c r="L44" s="4"/>
       <c r="M44" s="5">
-        <v>38622.383333333339</v>
+        <v>40353.950000000004</v>
       </c>
       <c r="N44" s="6">
-        <v>373</v>
+        <v>464</v>
       </c>
       <c r="O44" s="6">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="P44" s="7">
-        <v>4.9017271708683472</v>
+        <v>4.5593302483069982</v>
       </c>
       <c r="Q44" s="8">
-        <v>14.777134146341462</v>
+        <v>14.736587573964496</v>
       </c>
       <c r="R44" s="8">
-        <v>2.9988174193548387</v>
+        <v>3.01125</v>
       </c>
       <c r="S44" s="8">
         <v>7</v>
       </c>
       <c r="T44" s="9">
-        <v>0.54878048780487809</v>
+        <v>0.55621301775147924</v>
       </c>
       <c r="U44" s="9">
-        <v>0.097560975609756101</v>
+        <v>0.094674556213017749</v>
       </c>
       <c r="V44" s="9">
         <v>0</v>
@@ -8069,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="X44" s="9">
-        <v>0.012195121951219513</v>
+        <v>0.011834319526627219</v>
       </c>
       <c r="Y44" s="9">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA44" s="9">
-        <v>0.073170731707317069</v>
+        <v>0.071005917159763315</v>
       </c>
       <c r="AB44" s="9">
-        <v>0.012195121951219513</v>
+        <v>0.011834319526627219</v>
       </c>
       <c r="AC44" s="9">
         <v>0</v>
@@ -9666,7 +9666,7 @@
         <v>19649</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>51</v>
@@ -9695,79 +9695,79 @@
       </c>
       <c r="L55" s="4"/>
       <c r="M55" s="5">
-        <v>47192.821666666663</v>
+        <v>52961.279999999992</v>
       </c>
       <c r="N55" s="6">
-        <v>471</v>
+        <v>613</v>
       </c>
       <c r="O55" s="6">
-        <v>222</v>
+        <v>282</v>
       </c>
       <c r="P55" s="7">
-        <v>2.7074688741721857</v>
+        <v>2.8590757983193278</v>
       </c>
       <c r="Q55" s="8">
-        <v>16.178528828828828</v>
+        <v>15.892553546099291</v>
       </c>
       <c r="R55" s="8">
-        <v>6.2404301435406699</v>
+        <v>5.7892853383458647</v>
       </c>
       <c r="S55" s="8">
         <v>8</v>
       </c>
       <c r="T55" s="9">
-        <v>0.50450450450450446</v>
+        <v>0.52836879432624118</v>
       </c>
       <c r="U55" s="9">
-        <v>0.23423423423423423</v>
+        <v>0.21985815602836881</v>
       </c>
       <c r="V55" s="9">
-        <v>0.031531531531531529</v>
+        <v>0.028368794326241134</v>
       </c>
       <c r="W55" s="9">
         <v>0</v>
       </c>
       <c r="X55" s="9">
-        <v>0.14414414414414414</v>
+        <v>0.1276595744680851</v>
       </c>
       <c r="Y55" s="9">
-        <v>0.045045045045045043</v>
+        <v>0.039007092198581561</v>
       </c>
       <c r="Z55" s="9">
         <v>0</v>
       </c>
       <c r="AA55" s="9">
-        <v>0.085585585585585586</v>
+        <v>0.095744680851063829</v>
       </c>
       <c r="AB55" s="9">
-        <v>0.040540540540540543</v>
+        <v>0.031914893617021274</v>
       </c>
       <c r="AC55" s="9">
         <v>0</v>
       </c>
       <c r="AD55" s="6">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AE55" s="6">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="AF55" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG55" s="6">
         <v>0</v>
       </c>
       <c r="AH55" s="6">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AI55" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ55" s="6">
         <v>0</v>
       </c>
       <c r="AK55" s="6">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AL55" s="6">
         <v>9</v>
@@ -10228,7 +10228,7 @@
         <v>19657</v>
       </c>
       <c r="B59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C59" s="4">
         <v>51</v>
@@ -10259,61 +10259,61 @@
       </c>
       <c r="L59" s="4"/>
       <c r="M59" s="5">
-        <v>37286.654999999999</v>
+        <v>42969.440000000002</v>
       </c>
       <c r="N59" s="6">
-        <v>321</v>
+        <v>433</v>
       </c>
       <c r="O59" s="6">
-        <v>203</v>
+        <v>265</v>
       </c>
       <c r="P59" s="7">
-        <v>9.1216201238390102</v>
+        <v>9.4038489607390296</v>
       </c>
       <c r="Q59" s="8">
-        <v>26.791954187192118</v>
+        <v>28.31289320754717</v>
       </c>
       <c r="R59" s="8">
-        <v>10.9495</v>
+        <v>12.286068702290075</v>
       </c>
       <c r="S59" s="8">
         <v>7</v>
       </c>
       <c r="T59" s="9">
-        <v>0.098522167487684734</v>
+        <v>0.086792452830188674</v>
       </c>
       <c r="U59" s="9">
-        <v>0.26108374384236455</v>
+        <v>0.27169811320754716</v>
       </c>
       <c r="V59" s="9">
-        <v>0.029556650246305417</v>
+        <v>0.022641509433962263</v>
       </c>
       <c r="W59" s="9">
         <v>0</v>
       </c>
       <c r="X59" s="9">
-        <v>0.009852216748768473</v>
+        <v>0.011320754716981131</v>
       </c>
       <c r="Y59" s="9">
-        <v>0.009852216748768473</v>
+        <v>0.0075471698113207548</v>
       </c>
       <c r="Z59" s="9">
-        <v>0.009852216748768473</v>
+        <v>0.0075471698113207548</v>
       </c>
       <c r="AA59" s="9">
-        <v>0.014778325123152709</v>
+        <v>0.011320754716981131</v>
       </c>
       <c r="AB59" s="9">
-        <v>0.10837438423645321</v>
+        <v>0.10566037735849057</v>
       </c>
       <c r="AC59" s="9">
-        <v>0.11330049261083744</v>
+        <v>0.13584905660377358</v>
       </c>
       <c r="AD59" s="6">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AE59" s="6">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="AF59" s="6">
         <v>6</v>
@@ -10322,7 +10322,7 @@
         <v>0</v>
       </c>
       <c r="AH59" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI59" s="6">
         <v>2</v>
@@ -10334,10 +10334,10 @@
         <v>3</v>
       </c>
       <c r="AL59" s="6">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AM59" s="6">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AN59" s="9">
         <v>0</v>
@@ -10794,7 +10794,7 @@
         <v>19674</v>
       </c>
       <c r="B63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C63" s="4">
         <v>51</v>
@@ -10823,31 +10823,31 @@
       </c>
       <c r="L63" s="4"/>
       <c r="M63" s="5">
-        <v>43960.968333333331</v>
+        <v>42355.510000000002</v>
       </c>
       <c r="N63" s="6">
-        <v>445</v>
+        <v>500</v>
       </c>
       <c r="O63" s="6">
-        <v>286</v>
+        <v>326</v>
       </c>
       <c r="P63" s="7">
-        <v>5.3390389639639642</v>
+        <v>5.2546370967741938</v>
       </c>
       <c r="Q63" s="8">
-        <v>20.714277622377622</v>
+        <v>20.601687423312882</v>
       </c>
       <c r="R63" s="8">
-        <v>5.9304621722846438</v>
+        <v>5.9705850993377485</v>
       </c>
       <c r="S63" s="8">
         <v>10</v>
       </c>
       <c r="T63" s="9">
-        <v>0.23426573426573427</v>
+        <v>0.24233128834355827</v>
       </c>
       <c r="U63" s="9">
-        <v>0.22727272727272727</v>
+        <v>0.22392638036809817</v>
       </c>
       <c r="V63" s="9">
         <v>0</v>
@@ -10856,28 +10856,28 @@
         <v>0</v>
       </c>
       <c r="X63" s="9">
-        <v>0.034965034965034968</v>
+        <v>0.033742331288343558</v>
       </c>
       <c r="Y63" s="9">
-        <v>0.0034965034965034965</v>
+        <v>0.0030674846625766872</v>
       </c>
       <c r="Z63" s="9">
-        <v>0.006993006993006993</v>
+        <v>0.0061349693251533744</v>
       </c>
       <c r="AA63" s="9">
-        <v>0.15734265734265734</v>
+        <v>0.15950920245398773</v>
       </c>
       <c r="AB63" s="9">
-        <v>0.013986013986013986</v>
+        <v>0.012269938650306749</v>
       </c>
       <c r="AC63" s="9">
-        <v>0.027972027972027972</v>
+        <v>0.030674846625766871</v>
       </c>
       <c r="AD63" s="6">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AE63" s="6">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="AF63" s="6">
         <v>0</v>
@@ -10886,7 +10886,7 @@
         <v>0</v>
       </c>
       <c r="AH63" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI63" s="6">
         <v>1</v>
@@ -10895,13 +10895,13 @@
         <v>2</v>
       </c>
       <c r="AK63" s="6">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="AL63" s="6">
         <v>4</v>
       </c>
       <c r="AM63" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AN63" s="9">
         <v>0</v>
@@ -12242,7 +12242,7 @@
         <v>19694</v>
       </c>
       <c r="B73" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C73" s="4">
         <v>51</v>
@@ -12273,61 +12273,61 @@
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="5">
-        <v>41503.816666666673</v>
+        <v>45400.590000000004</v>
       </c>
       <c r="N73" s="6">
-        <v>377</v>
+        <v>480</v>
       </c>
       <c r="O73" s="6">
-        <v>266</v>
+        <v>346</v>
       </c>
       <c r="P73" s="7">
-        <v>10.870098128342246</v>
+        <v>9.9846262054507324</v>
       </c>
       <c r="Q73" s="8">
-        <v>37.445338697318007</v>
+        <v>35.364614076246333</v>
       </c>
       <c r="R73" s="8">
-        <v>19.378617441860463</v>
+        <v>18.361770326409495</v>
       </c>
       <c r="S73" s="8">
         <v>7</v>
       </c>
       <c r="T73" s="9">
-        <v>0.057471264367816091</v>
+        <v>0.055718475073313782</v>
       </c>
       <c r="U73" s="9">
-        <v>0.13157894736842105</v>
+        <v>0.12716763005780346</v>
       </c>
       <c r="V73" s="9">
-        <v>0.052631578947368418</v>
+        <v>0.04046242774566474</v>
       </c>
       <c r="W73" s="9">
         <v>0</v>
       </c>
       <c r="X73" s="9">
-        <v>0.022556390977443608</v>
+        <v>0.017341040462427744</v>
       </c>
       <c r="Y73" s="9">
-        <v>0.0037593984962406013</v>
+        <v>0.0028901734104046241</v>
       </c>
       <c r="Z73" s="9">
         <v>0</v>
       </c>
       <c r="AA73" s="9">
-        <v>0.011278195488721804</v>
+        <v>0.011560693641618497</v>
       </c>
       <c r="AB73" s="9">
-        <v>0.0075187969924812026</v>
+        <v>0.011560693641618497</v>
       </c>
       <c r="AC73" s="9">
-        <v>0.063909774436090222</v>
+        <v>0.066473988439306353</v>
       </c>
       <c r="AD73" s="6">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="AE73" s="6">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="AF73" s="6">
         <v>14</v>
@@ -12345,13 +12345,13 @@
         <v>0</v>
       </c>
       <c r="AK73" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL73" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM73" s="6">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AN73" s="9">
         <v>0</v>
@@ -13124,7 +13124,7 @@
         <v>19715</v>
       </c>
       <c r="B79" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C79" s="4">
         <v>51</v>
@@ -13155,40 +13155,40 @@
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="5">
-        <v>41327.125</v>
+        <v>45795.970000000008</v>
       </c>
       <c r="N79" s="6">
-        <v>380</v>
+        <v>488</v>
       </c>
       <c r="O79" s="6">
-        <v>244</v>
+        <v>313</v>
       </c>
       <c r="P79" s="7">
-        <v>10.671378795811519</v>
+        <v>10.634972745901639</v>
       </c>
       <c r="Q79" s="8">
-        <v>29.682991803278686</v>
+        <v>29.712779552715656</v>
       </c>
       <c r="R79" s="8">
-        <v>10.182304115226337</v>
+        <v>10.075294533762058</v>
       </c>
       <c r="S79" s="8">
         <v>9</v>
       </c>
       <c r="T79" s="9">
-        <v>0.061475409836065573</v>
+        <v>0.051118210862619806</v>
       </c>
       <c r="U79" s="9">
-        <v>0.15163934426229508</v>
+        <v>0.18849840255591055</v>
       </c>
       <c r="V79" s="9">
-        <v>0</v>
+        <v>0.0031948881789137379</v>
       </c>
       <c r="W79" s="9">
         <v>0</v>
       </c>
       <c r="X79" s="9">
-        <v>0.069672131147540978</v>
+        <v>0.054313099041533544</v>
       </c>
       <c r="Y79" s="9">
         <v>0</v>
@@ -13197,22 +13197,22 @@
         <v>0</v>
       </c>
       <c r="AA79" s="9">
-        <v>0.0040983606557377051</v>
+        <v>0.0095846645367412137</v>
       </c>
       <c r="AB79" s="9">
-        <v>0.086065573770491802</v>
+        <v>0.12779552715654952</v>
       </c>
       <c r="AC79" s="9">
         <v>0</v>
       </c>
       <c r="AD79" s="6">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="AE79" s="6">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="AF79" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG79" s="6">
         <v>0</v>
@@ -13227,10 +13227,10 @@
         <v>0</v>
       </c>
       <c r="AK79" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL79" s="6">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="AM79" s="6">
         <v>0</v>
@@ -14417,7 +14417,7 @@
         <v>19730</v>
       </c>
       <c r="B88" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C88" s="4">
         <v>51</v>
@@ -14446,40 +14446,40 @@
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="5">
-        <v>55610.053333333337</v>
+        <v>60363.690000000002</v>
       </c>
       <c r="N88" s="6">
-        <v>481</v>
+        <v>619</v>
       </c>
       <c r="O88" s="6">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="P88" s="7">
-        <v>4.6924708418891168</v>
+        <v>4.7800637958532697</v>
       </c>
       <c r="Q88" s="8">
-        <v>23.505434057971012</v>
+        <v>23.089938414634144</v>
       </c>
       <c r="R88" s="8">
-        <v>10.530676811594203</v>
+        <v>10.157927439024391</v>
       </c>
       <c r="S88" s="8">
         <v>8</v>
       </c>
       <c r="T88" s="9">
-        <v>0.17391304347826086</v>
+        <v>0.1524390243902439</v>
       </c>
       <c r="U88" s="9">
-        <v>0.54347826086956519</v>
+        <v>0.5</v>
       </c>
       <c r="V88" s="9">
-        <v>0.20289855072463769</v>
+        <v>0.17073170731707318</v>
       </c>
       <c r="W88" s="9">
         <v>0</v>
       </c>
       <c r="X88" s="9">
-        <v>0.043478260869565216</v>
+        <v>0.036585365853658534</v>
       </c>
       <c r="Y88" s="9">
         <v>0</v>
@@ -14488,19 +14488,19 @@
         <v>0</v>
       </c>
       <c r="AA88" s="9">
-        <v>0.007246376811594203</v>
+        <v>0.0060975609756097563</v>
       </c>
       <c r="AB88" s="9">
-        <v>0.10144927536231885</v>
+        <v>0.10365853658536585</v>
       </c>
       <c r="AC88" s="9">
-        <v>0.27536231884057971</v>
+        <v>0.25609756097560976</v>
       </c>
       <c r="AD88" s="6">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="AE88" s="6">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AF88" s="6">
         <v>28</v>
@@ -14521,10 +14521,10 @@
         <v>1</v>
       </c>
       <c r="AL88" s="6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AM88" s="6">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AN88" s="9">
         <v>0</v>
@@ -15764,7 +15764,7 @@
         <v>19749</v>
       </c>
       <c r="B97" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C97" s="4">
         <v>51</v>
@@ -15793,70 +15793,70 @@
       </c>
       <c r="L97" s="4"/>
       <c r="M97" s="5">
-        <v>25463.514999999999</v>
+        <v>26916.73</v>
       </c>
       <c r="N97" s="6">
-        <v>222</v>
+        <v>272</v>
       </c>
       <c r="O97" s="6">
-        <v>138</v>
+        <v>171</v>
       </c>
       <c r="P97" s="7">
-        <v>4.0960031674208146</v>
+        <v>4.5509914498141262</v>
       </c>
       <c r="Q97" s="8">
-        <v>21.850483333333333</v>
+        <v>23.265789473684208</v>
       </c>
       <c r="R97" s="8">
-        <v>9.9660591240875913</v>
+        <v>11.026275294117646</v>
       </c>
       <c r="S97" s="8">
         <v>8</v>
       </c>
       <c r="T97" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.13450292397660818</v>
       </c>
       <c r="U97" s="9">
-        <v>0.10869565217391304</v>
+        <v>0.11695906432748537</v>
       </c>
       <c r="V97" s="9">
-        <v>0.036231884057971016</v>
+        <v>0.040935672514619881</v>
       </c>
       <c r="W97" s="9">
-        <v>0</v>
+        <v>0.0058479532160000004</v>
       </c>
       <c r="X97" s="9">
-        <v>0.043478260869565216</v>
+        <v>0.046783625730994149</v>
       </c>
       <c r="Y97" s="9">
-        <v>0.007246376811594203</v>
+        <v>0.0058479532163742687</v>
       </c>
       <c r="Z97" s="9">
-        <v>0.014492753623188406</v>
+        <v>0.011695906432748537</v>
       </c>
       <c r="AA97" s="9">
-        <v>0.021739130434782608</v>
+        <v>0.017543859649122806</v>
       </c>
       <c r="AB97" s="9">
         <v>0</v>
       </c>
       <c r="AC97" s="9">
-        <v>0.014492753623188406</v>
+        <v>0.023391812865497075</v>
       </c>
       <c r="AD97" s="6">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AE97" s="6">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AF97" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG97" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH97" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI97" s="6">
         <v>1</v>
@@ -15871,7 +15871,7 @@
         <v>0</v>
       </c>
       <c r="AM97" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN97" s="9">
         <v>0</v>
@@ -18272,7 +18272,7 @@
         <v>19785</v>
       </c>
       <c r="B113" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C113" s="4">
         <v>51</v>
@@ -18303,64 +18303,64 @@
       </c>
       <c r="L113" s="4"/>
       <c r="M113" s="5">
-        <v>28691.623333333333</v>
+        <v>32935.220000000001</v>
       </c>
       <c r="N113" s="6">
-        <v>236</v>
+        <v>313</v>
       </c>
       <c r="O113" s="6">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="P113" s="7">
-        <v>5.9534901709401709</v>
+        <v>6.0343012903225803</v>
       </c>
       <c r="Q113" s="8">
-        <v>17.999347058823528</v>
+        <v>18.645896268656717</v>
       </c>
       <c r="R113" s="8">
-        <v>6.0622340425531913</v>
+        <v>6.8461745901639341</v>
       </c>
       <c r="S113" s="8">
         <v>7</v>
       </c>
       <c r="T113" s="9">
-        <v>0.48039215686274511</v>
+        <v>0.47761194029850745</v>
       </c>
       <c r="U113" s="9">
-        <v>0.40196078431372551</v>
+        <v>0.40298507462686567</v>
       </c>
       <c r="V113" s="9">
-        <v>0.039215686274509803</v>
+        <v>0.037313432835820892</v>
       </c>
       <c r="W113" s="9">
-        <v>0.0098039215679999996</v>
+        <v>0.0074626865670000004</v>
       </c>
       <c r="X113" s="9">
-        <v>0.029411764705882353</v>
+        <v>0.022388059701492536</v>
       </c>
       <c r="Y113" s="9">
-        <v>0.0098039215686274508</v>
+        <v>0.007462686567164179</v>
       </c>
       <c r="Z113" s="9">
         <v>0</v>
       </c>
       <c r="AA113" s="9">
-        <v>0.30392156862745096</v>
+        <v>0.32089552238805968</v>
       </c>
       <c r="AB113" s="9">
-        <v>0.0098039215686274508</v>
+        <v>0.007462686567164179</v>
       </c>
       <c r="AC113" s="9">
-        <v>0.058823529411764705</v>
+        <v>0.044776119402985072</v>
       </c>
       <c r="AD113" s="6">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="AE113" s="6">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="AF113" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG113" s="6">
         <v>1</v>
@@ -18375,7 +18375,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="6">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="AL113" s="6">
         <v>1</v>
@@ -20030,7 +20030,7 @@
         <v>19842</v>
       </c>
       <c r="B125" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C125" s="4">
         <v>51</v>
@@ -20061,85 +20061,85 @@
       </c>
       <c r="L125" s="4"/>
       <c r="M125" s="5">
-        <v>69492.768333333341</v>
+        <v>73176.419999999998</v>
       </c>
       <c r="N125" s="6">
-        <v>575</v>
+        <v>704</v>
       </c>
       <c r="O125" s="6">
-        <v>371</v>
+        <v>470</v>
       </c>
       <c r="P125" s="7">
-        <v>5.2493296160877509</v>
+        <v>5.6162474852071007</v>
       </c>
       <c r="Q125" s="8">
-        <v>23.108266037735849</v>
+        <v>24.334610000000001</v>
       </c>
       <c r="R125" s="8">
-        <v>10.803698314606741</v>
+        <v>12.127111538461538</v>
       </c>
       <c r="S125" s="8">
         <v>8</v>
       </c>
       <c r="T125" s="9">
-        <v>0.080862533692722366</v>
+        <v>0.091489361702127653</v>
       </c>
       <c r="U125" s="9">
-        <v>0.12668463611859837</v>
+        <v>0.13617021276595745</v>
       </c>
       <c r="V125" s="9">
-        <v>0.053908355795148251</v>
+        <v>0.053191489361702128</v>
       </c>
       <c r="W125" s="9">
-        <v>0.016172506738000001</v>
+        <v>0.040425531914000001</v>
       </c>
       <c r="X125" s="9">
-        <v>0.024258760107816711</v>
+        <v>0.021276595744680851</v>
       </c>
       <c r="Y125" s="9">
-        <v>0.032345013477088951</v>
+        <v>0.053191489361702128</v>
       </c>
       <c r="Z125" s="9">
-        <v>0.0026954177897574125</v>
+        <v>0.0021276595744680851</v>
       </c>
       <c r="AA125" s="9">
-        <v>0.040431266846361183</v>
+        <v>0.059574468085106386</v>
       </c>
       <c r="AB125" s="9">
-        <v>0.029649595687331536</v>
+        <v>0.023404255319148935</v>
       </c>
       <c r="AC125" s="9">
-        <v>0</v>
+        <v>0.0042553191489361703</v>
       </c>
       <c r="AD125" s="6">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="AE125" s="6">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="AF125" s="6">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AG125" s="6">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AH125" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI125" s="6">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AJ125" s="6">
         <v>1</v>
       </c>
       <c r="AK125" s="6">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="AL125" s="6">
         <v>11</v>
       </c>
       <c r="AM125" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN125" s="9">
         <v>0</v>
@@ -20224,7 +20224,7 @@
         <v>282</v>
       </c>
       <c r="O126" s="6">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="P126" s="7">
         <v>3.6472024999999997</v>
@@ -20242,46 +20242,46 @@
         <v>0.28387096774193549</v>
       </c>
       <c r="U126" s="9">
-        <v>0.33628318584070799</v>
+        <v>0.34193548387096773</v>
       </c>
       <c r="V126" s="9">
-        <v>0.088495575221238937</v>
+        <v>0.070967741935483872</v>
       </c>
       <c r="W126" s="9">
         <v>0</v>
       </c>
       <c r="X126" s="9">
-        <v>0.19469026548672566</v>
+        <v>0.15483870967741936</v>
       </c>
       <c r="Y126" s="9">
-        <v>0.026548672566371681</v>
+        <v>0.01935483870967742</v>
       </c>
       <c r="Z126" s="9">
         <v>0</v>
       </c>
       <c r="AA126" s="9">
-        <v>0.13274336283185842</v>
+        <v>0.10967741935483871</v>
       </c>
       <c r="AB126" s="9">
-        <v>0</v>
+        <v>0.0064516129032258064</v>
       </c>
       <c r="AC126" s="9">
-        <v>0.035398230088495575</v>
+        <v>0.077419354838709681</v>
       </c>
       <c r="AD126" s="6">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="AE126" s="6">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="AF126" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG126" s="6">
         <v>0</v>
       </c>
       <c r="AH126" s="6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI126" s="6">
         <v>3</v>
@@ -20290,19 +20290,19 @@
         <v>0</v>
       </c>
       <c r="AK126" s="6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL126" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM126" s="6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AN126" s="9">
-        <v>0.017699115044247787</v>
+        <v>0.01935483870967742</v>
       </c>
       <c r="AO126" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c t="s" r="AP126" s="4">
         <v>58</v>
@@ -20501,7 +20501,7 @@
         <v>19859</v>
       </c>
       <c r="B128" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C128" s="4">
         <v>51</v>
@@ -20532,61 +20532,61 @@
       </c>
       <c r="L128" s="4"/>
       <c r="M128" s="5">
-        <v>31149.031666666666</v>
+        <v>33140.529999999999</v>
       </c>
       <c r="N128" s="6">
-        <v>278</v>
+        <v>342</v>
       </c>
       <c r="O128" s="6">
-        <v>225</v>
+        <v>277</v>
       </c>
       <c r="P128" s="7">
-        <v>7.7264039426523308</v>
+        <v>8.4790574344023319</v>
       </c>
       <c r="Q128" s="8">
-        <v>21.516518222222221</v>
+        <v>22.525511191335742</v>
       </c>
       <c r="R128" s="8">
-        <v>6.4111848888888883</v>
+        <v>6.6187122743682307</v>
       </c>
       <c r="S128" s="8">
         <v>7</v>
       </c>
       <c r="T128" s="9">
-        <v>0.26222222222222225</v>
+        <v>0.22743682310469315</v>
       </c>
       <c r="U128" s="9">
-        <v>0.035555555555555556</v>
+        <v>0.032490974729241874</v>
       </c>
       <c r="V128" s="9">
-        <v>0.0044444444444444444</v>
+        <v>0.0036101083032490976</v>
       </c>
       <c r="W128" s="9">
         <v>0</v>
       </c>
       <c r="X128" s="9">
-        <v>0.013333333333333334</v>
+        <v>0.010830324909747292</v>
       </c>
       <c r="Y128" s="9">
         <v>0</v>
       </c>
       <c r="Z128" s="9">
-        <v>0.0044444444444444444</v>
+        <v>0.0072202166064981952</v>
       </c>
       <c r="AA128" s="9">
         <v>0</v>
       </c>
       <c r="AB128" s="9">
-        <v>0.0044444444444444444</v>
+        <v>0.0036101083032490976</v>
       </c>
       <c r="AC128" s="9">
-        <v>0.0088888888888888889</v>
+        <v>0.0072202166064981952</v>
       </c>
       <c r="AD128" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE128" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF128" s="6">
         <v>1</v>
@@ -20601,7 +20601,7 @@
         <v>0</v>
       </c>
       <c r="AJ128" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK128" s="6">
         <v>0</v>
@@ -21749,7 +21749,7 @@
         <v>19881</v>
       </c>
       <c r="B136" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C136" s="4">
         <v>51</v>
@@ -21780,70 +21780,70 @@
       </c>
       <c r="L136" s="4"/>
       <c r="M136" s="5">
-        <v>78422.014999999999</v>
+        <v>83003.489999999991</v>
       </c>
       <c r="N136" s="6">
-        <v>584</v>
+        <v>724</v>
       </c>
       <c r="O136" s="6">
-        <v>429</v>
+        <v>526</v>
       </c>
       <c r="P136" s="7">
-        <v>3.1209524369747896</v>
+        <v>3.1766531250000001</v>
       </c>
       <c r="Q136" s="8">
-        <v>20.42253333333333</v>
+        <v>19.870754372623573</v>
       </c>
       <c r="R136" s="8">
-        <v>11.450879136690647</v>
+        <v>10.791018093385215</v>
       </c>
       <c r="S136" s="8">
         <v>6.2999999999999998</v>
       </c>
       <c r="T136" s="9">
-        <v>0.31934731934731936</v>
+        <v>0.32319391634980987</v>
       </c>
       <c r="U136" s="9">
-        <v>0.10023310023310024</v>
+        <v>0.093155893536121678</v>
       </c>
       <c r="V136" s="9">
-        <v>0.053613053613053616</v>
+        <v>0.049429657794676805</v>
       </c>
       <c r="W136" s="9">
-        <v>0.002331002331</v>
+        <v>0.001901140684</v>
       </c>
       <c r="X136" s="9">
-        <v>0.013986013986013986</v>
+        <v>0.017110266159695818</v>
       </c>
       <c r="Y136" s="9">
-        <v>0.013986013986013986</v>
+        <v>0.011406844106463879</v>
       </c>
       <c r="Z136" s="9">
         <v>0</v>
       </c>
       <c r="AA136" s="9">
-        <v>0.032634032634032632</v>
+        <v>0.026615969581749048</v>
       </c>
       <c r="AB136" s="9">
-        <v>0.006993006993006993</v>
+        <v>0.0057034220532319393</v>
       </c>
       <c r="AC136" s="9">
-        <v>0.013986013986013986</v>
+        <v>0.011406844106463879</v>
       </c>
       <c r="AD136" s="6">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="AE136" s="6">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="AF136" s="6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AG136" s="6">
         <v>1</v>
       </c>
       <c r="AH136" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AI136" s="6">
         <v>6</v>
@@ -22063,7 +22063,7 @@
         <v>19884</v>
       </c>
       <c r="B138" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C138" s="4">
         <v>51</v>
@@ -22094,31 +22094,31 @@
       </c>
       <c r="L138" s="4"/>
       <c r="M138" s="5">
-        <v>28110.740000000002</v>
+        <v>30369.779999999999</v>
       </c>
       <c r="N138" s="6">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="O138" s="6">
-        <v>191</v>
+        <v>242</v>
       </c>
       <c r="P138" s="7">
-        <v>8.3418503676470586</v>
+        <v>8.1235119047619051</v>
       </c>
       <c r="Q138" s="8">
-        <v>22.418499476439791</v>
+        <v>22.579407851239669</v>
       </c>
       <c r="R138" s="8">
-        <v>7.3381392638036811</v>
+        <v>7.931984285714285</v>
       </c>
       <c r="S138" s="8">
         <v>7</v>
       </c>
       <c r="T138" s="9">
-        <v>0.25654450261780104</v>
+        <v>0.21900826446280991</v>
       </c>
       <c r="U138" s="9">
-        <v>0.18848167539267016</v>
+        <v>0.16528925619834711</v>
       </c>
       <c r="V138" s="9">
         <v>0</v>
@@ -22127,28 +22127,28 @@
         <v>0</v>
       </c>
       <c r="X138" s="9">
-        <v>0.010471204188481676</v>
+        <v>0.0082644628099173556</v>
       </c>
       <c r="Y138" s="9">
-        <v>0.005235602094240838</v>
+        <v>0.0082644628099173556</v>
       </c>
       <c r="Z138" s="9">
         <v>0</v>
       </c>
       <c r="AA138" s="9">
-        <v>0.16753926701570682</v>
+        <v>0.1487603305785124</v>
       </c>
       <c r="AB138" s="9">
-        <v>0.015706806282722512</v>
+        <v>0.012396694214876033</v>
       </c>
       <c r="AC138" s="9">
-        <v>0.010471204188481676</v>
+        <v>0.0082644628099173556</v>
       </c>
       <c r="AD138" s="6">
+        <v>45</v>
+      </c>
+      <c r="AE138" s="6">
         <v>40</v>
-      </c>
-      <c r="AE138" s="6">
-        <v>36</v>
       </c>
       <c r="AF138" s="6">
         <v>0</v>
@@ -22160,13 +22160,13 @@
         <v>2</v>
       </c>
       <c r="AI138" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ138" s="6">
         <v>0</v>
       </c>
       <c r="AK138" s="6">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AL138" s="6">
         <v>3</v>
@@ -23292,7 +23292,7 @@
         <v>184</v>
       </c>
       <c r="O146" s="6">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="P146" s="7">
         <v>5.4594354497354498</v>
@@ -23310,7 +23310,7 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="U146" s="9">
-        <v>0.45454545454545453</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="V146" s="9">
         <v>0</v>
@@ -23319,7 +23319,7 @@
         <v>0</v>
       </c>
       <c r="X146" s="9">
-        <v>0.090909090909090912</v>
+        <v>0.044444444444444446</v>
       </c>
       <c r="Y146" s="9">
         <v>0</v>
@@ -23328,19 +23328,19 @@
         <v>0</v>
       </c>
       <c r="AA146" s="9">
-        <v>0</v>
+        <v>0.066666666666666666</v>
       </c>
       <c r="AB146" s="9">
-        <v>0.090909090909090912</v>
+        <v>0.088888888888888892</v>
       </c>
       <c r="AC146" s="9">
-        <v>0.36363636363636365</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="AD146" s="6">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="AE146" s="6">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="AF146" s="6">
         <v>0</v>
@@ -23349,7 +23349,7 @@
         <v>0</v>
       </c>
       <c r="AH146" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI146" s="6">
         <v>0</v>
@@ -23358,13 +23358,13 @@
         <v>0</v>
       </c>
       <c r="AK146" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL146" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AM146" s="6">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AN146" s="9">
         <v>0</v>
@@ -23412,7 +23412,7 @@
         <v>19910</v>
       </c>
       <c r="B147" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C147" s="4">
         <v>51</v>
@@ -23443,40 +23443,40 @@
       </c>
       <c r="L147" s="4"/>
       <c r="M147" s="5">
-        <v>26328.890000000003</v>
+        <v>28913.370000000003</v>
       </c>
       <c r="N147" s="6">
-        <v>256</v>
+        <v>318</v>
       </c>
       <c r="O147" s="6">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="P147" s="7">
-        <v>5.7935898785425097</v>
+        <v>5.2996226537216824</v>
       </c>
       <c r="Q147" s="8">
-        <v>17.1565700729927</v>
+        <v>15.721443274853799</v>
       </c>
       <c r="R147" s="8">
-        <v>9.7361523076923078</v>
+        <v>8.6948189189189193</v>
       </c>
       <c r="S147" s="8">
         <v>8</v>
       </c>
       <c r="T147" s="9">
-        <v>0.65693430656934304</v>
+        <v>0.70760233918128657</v>
       </c>
       <c r="U147" s="9">
-        <v>0.69565217391304346</v>
+        <v>0.71511627906976749</v>
       </c>
       <c r="V147" s="9">
-        <v>0.014492753623188406</v>
+        <v>0.011627906976744186</v>
       </c>
       <c r="W147" s="9">
         <v>0</v>
       </c>
       <c r="X147" s="9">
-        <v>0.014492753623188406</v>
+        <v>0.023255813953488372</v>
       </c>
       <c r="Y147" s="9">
         <v>0</v>
@@ -23485,19 +23485,19 @@
         <v>0</v>
       </c>
       <c r="AA147" s="9">
-        <v>0.65217391304347827</v>
+        <v>0.68023255813953487</v>
       </c>
       <c r="AB147" s="9">
-        <v>0.021739130434782608</v>
+        <v>0.017441860465116279</v>
       </c>
       <c r="AC147" s="9">
-        <v>0.043478260869565216</v>
+        <v>0.046511627906976744</v>
       </c>
       <c r="AD147" s="6">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="AE147" s="6">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="AF147" s="6">
         <v>2</v>
@@ -23506,7 +23506,7 @@
         <v>0</v>
       </c>
       <c r="AH147" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI147" s="6">
         <v>0</v>
@@ -23515,13 +23515,13 @@
         <v>0</v>
       </c>
       <c r="AK147" s="6">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="AL147" s="6">
         <v>3</v>
       </c>
       <c r="AM147" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN147" s="9">
         <v>0</v>
@@ -24296,7 +24296,7 @@
         <v>19927</v>
       </c>
       <c r="B153" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C153" s="4">
         <v>51</v>
@@ -24327,40 +24327,40 @@
       </c>
       <c r="L153" s="4"/>
       <c r="M153" s="5">
-        <v>11583.495000000001</v>
+        <v>12024.689999999999</v>
       </c>
       <c r="N153" s="6">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="O153" s="6">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="P153" s="7">
-        <v>9.8776452380952389</v>
+        <v>9.3715363636363627</v>
       </c>
       <c r="Q153" s="8">
-        <v>29.303288157894738</v>
+        <v>27.371286138613858</v>
       </c>
       <c r="R153" s="8">
-        <v>13.110086842105263</v>
+        <v>11.936833</v>
       </c>
       <c r="S153" s="8">
         <v>7</v>
       </c>
       <c r="T153" s="9">
-        <v>0.13157894736842105</v>
+        <v>0.16831683168316833</v>
       </c>
       <c r="U153" s="9">
-        <v>0.18421052631578946</v>
+        <v>0.20792079207920791</v>
       </c>
       <c r="V153" s="9">
-        <v>0.078947368421052627</v>
+        <v>0.099009900990099015</v>
       </c>
       <c r="W153" s="9">
         <v>0</v>
       </c>
       <c r="X153" s="9">
-        <v>0.052631578947368418</v>
+        <v>0.049504950495049507</v>
       </c>
       <c r="Y153" s="9">
         <v>0</v>
@@ -24369,28 +24369,28 @@
         <v>0</v>
       </c>
       <c r="AA153" s="9">
-        <v>0.013157894736842105</v>
+        <v>0.029702970297029702</v>
       </c>
       <c r="AB153" s="9">
-        <v>0.013157894736842105</v>
+        <v>0.019801980198019802</v>
       </c>
       <c r="AC153" s="9">
-        <v>0.026315789473684209</v>
+        <v>0.019801980198019802</v>
       </c>
       <c r="AD153" s="6">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AE153" s="6">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AF153" s="6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG153" s="6">
         <v>0</v>
       </c>
       <c r="AH153" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI153" s="6">
         <v>0</v>
@@ -24399,10 +24399,10 @@
         <v>0</v>
       </c>
       <c r="AK153" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL153" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM153" s="6">
         <v>2</v>
@@ -24610,7 +24610,7 @@
         <v>19930</v>
       </c>
       <c r="B155" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C155" s="4">
         <v>51</v>
@@ -24641,61 +24641,61 @@
       </c>
       <c r="L155" s="4"/>
       <c r="M155" s="5">
-        <v>29553.883333333335</v>
+        <v>32817.75</v>
       </c>
       <c r="N155" s="6">
-        <v>372</v>
+        <v>489</v>
       </c>
       <c r="O155" s="6">
-        <v>318</v>
+        <v>431</v>
       </c>
       <c r="P155" s="7">
-        <v>4.7876114973262034</v>
+        <v>4.7551596741344193</v>
       </c>
       <c r="Q155" s="8">
-        <v>21.946173899371072</v>
+        <v>22.002474709976799</v>
       </c>
       <c r="R155" s="8">
-        <v>11.285649830508476</v>
+        <v>11.151474201474201</v>
       </c>
       <c r="S155" s="8">
         <v>7</v>
       </c>
       <c r="T155" s="9">
-        <v>0.19496855345911951</v>
+        <v>0.16705336426914152</v>
       </c>
       <c r="U155" s="9">
-        <v>0.48742138364779874</v>
+        <v>0.42459396751740142</v>
       </c>
       <c r="V155" s="9">
-        <v>0.015723270440251572</v>
+        <v>0.011600928074245939</v>
       </c>
       <c r="W155" s="9">
         <v>0</v>
       </c>
       <c r="X155" s="9">
-        <v>0.025157232704402517</v>
+        <v>0.027842227378190254</v>
       </c>
       <c r="Y155" s="9">
-        <v>0.0220125786163522</v>
+        <v>0.016241299303944315</v>
       </c>
       <c r="Z155" s="9">
-        <v>0.0031446540880503146</v>
+        <v>0.0023201856148491878</v>
       </c>
       <c r="AA155" s="9">
-        <v>0.078616352201257858</v>
+        <v>0.060324825986078884</v>
       </c>
       <c r="AB155" s="9">
-        <v>0.034591194968553458</v>
+        <v>0.025522041763341066</v>
       </c>
       <c r="AC155" s="9">
-        <v>0.37421383647798739</v>
+        <v>0.33178654292343385</v>
       </c>
       <c r="AD155" s="6">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="AE155" s="6">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="AF155" s="6">
         <v>5</v>
@@ -24704,7 +24704,7 @@
         <v>0</v>
       </c>
       <c r="AH155" s="6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AI155" s="6">
         <v>7</v>
@@ -24713,13 +24713,13 @@
         <v>1</v>
       </c>
       <c r="AK155" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL155" s="6">
         <v>11</v>
       </c>
       <c r="AM155" s="6">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="AN155" s="9">
         <v>0</v>
@@ -24767,7 +24767,7 @@
         <v>19931</v>
       </c>
       <c r="B156" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C156" s="4">
         <v>51</v>
@@ -24798,82 +24798,82 @@
       </c>
       <c r="L156" s="4"/>
       <c r="M156" s="5">
-        <v>32129.264999999999</v>
+        <v>38774.639999999999</v>
       </c>
       <c r="N156" s="6">
-        <v>289</v>
+        <v>408</v>
       </c>
       <c r="O156" s="6">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="P156" s="7">
-        <v>4.8154255319148938</v>
+        <v>4.7554020100502514</v>
       </c>
       <c r="Q156" s="8">
-        <v>16.492147933884297</v>
+        <v>16.282434730538924</v>
       </c>
       <c r="R156" s="8">
-        <v>4.6387461538461539</v>
+        <v>4.5362316770186339</v>
       </c>
       <c r="S156" s="8">
         <v>7</v>
       </c>
       <c r="T156" s="9">
-        <v>0.49586776859504134</v>
+        <v>0.48502994011976047</v>
       </c>
       <c r="U156" s="9">
-        <v>0.11570247933884298</v>
+        <v>0.1377245508982036</v>
       </c>
       <c r="V156" s="9">
-        <v>0.016528925619834711</v>
+        <v>0.023952095808383235</v>
       </c>
       <c r="W156" s="9">
         <v>0</v>
       </c>
       <c r="X156" s="9">
-        <v>0.016528925619834711</v>
+        <v>0.035928143712574849</v>
       </c>
       <c r="Y156" s="9">
-        <v>0.0082644628099173556</v>
+        <v>0.011976047904191617</v>
       </c>
       <c r="Z156" s="9">
-        <v>0.0082644628099173556</v>
+        <v>0.0059880239520958087</v>
       </c>
       <c r="AA156" s="9">
-        <v>0.0743801652892562</v>
+        <v>0.083832335329341312</v>
       </c>
       <c r="AB156" s="9">
-        <v>0.0082644628099173556</v>
+        <v>0.029940119760479042</v>
       </c>
       <c r="AC156" s="9">
         <v>0</v>
       </c>
       <c r="AD156" s="6">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="AE156" s="6">
+        <v>23</v>
+      </c>
+      <c r="AF156" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG156" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH156" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI156" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ156" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK156" s="6">
         <v>14</v>
       </c>
-      <c r="AF156" s="6">
-        <v>2</v>
-      </c>
-      <c r="AG156" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH156" s="6">
-        <v>2</v>
-      </c>
-      <c r="AI156" s="6">
-        <v>1</v>
-      </c>
-      <c r="AJ156" s="6">
-        <v>1</v>
-      </c>
-      <c r="AK156" s="6">
-        <v>9</v>
-      </c>
       <c r="AL156" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AM156" s="6">
         <v>0</v>
@@ -25393,7 +25393,7 @@
         <v>19943</v>
       </c>
       <c r="B160" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C160" s="4">
         <v>51</v>
@@ -25424,40 +25424,40 @@
       </c>
       <c r="L160" s="4"/>
       <c r="M160" s="5">
-        <v>19532.286666666667</v>
+        <v>22529.470000000001</v>
       </c>
       <c r="N160" s="6">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="O160" s="6">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="P160" s="7">
-        <v>8.4936929729729727</v>
+        <v>9.1829955465587041</v>
       </c>
       <c r="Q160" s="8">
-        <v>28.19575964912281</v>
+        <v>26.940362585034013</v>
       </c>
       <c r="R160" s="8">
-        <v>14.052827678571429</v>
+        <v>12.660763888888889</v>
       </c>
       <c r="S160" s="8">
         <v>7</v>
       </c>
       <c r="T160" s="9">
-        <v>0.20175438596491227</v>
+        <v>0.20408163265306123</v>
       </c>
       <c r="U160" s="9">
-        <v>0.21052631578947367</v>
+        <v>0.22448979591836735</v>
       </c>
       <c r="V160" s="9">
-        <v>0.052631578947368418</v>
+        <v>0.061224489795918366</v>
       </c>
       <c r="W160" s="9">
         <v>0</v>
       </c>
       <c r="X160" s="9">
-        <v>0.061403508771929821</v>
+        <v>0.061224489795918366</v>
       </c>
       <c r="Y160" s="9">
         <v>0</v>
@@ -25466,28 +25466,28 @@
         <v>0</v>
       </c>
       <c r="AA160" s="9">
-        <v>0.026315789473684209</v>
+        <v>0.027210884353741496</v>
       </c>
       <c r="AB160" s="9">
-        <v>0.017543859649122806</v>
+        <v>0.027210884353741496</v>
       </c>
       <c r="AC160" s="9">
-        <v>0.08771929824561403</v>
+        <v>0.081632653061224483</v>
       </c>
       <c r="AD160" s="6">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AE160" s="6">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="AF160" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG160" s="6">
         <v>0</v>
       </c>
       <c r="AH160" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI160" s="6">
         <v>0</v>
@@ -25496,13 +25496,13 @@
         <v>0</v>
       </c>
       <c r="AK160" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL160" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM160" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AN160" s="9">
         <v>0</v>
@@ -26178,7 +26178,7 @@
         <v>19951</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26209,61 +26209,61 @@
       </c>
       <c r="L165" s="4"/>
       <c r="M165" s="5">
-        <v>29505.688333333335</v>
+        <v>35190.650000000001</v>
       </c>
       <c r="N165" s="6">
-        <v>256</v>
+        <v>358</v>
       </c>
       <c r="O165" s="6">
-        <v>138</v>
+        <v>192</v>
       </c>
       <c r="P165" s="7">
-        <v>4.6653440476190475</v>
+        <v>5.3391573863636363</v>
       </c>
       <c r="Q165" s="8">
-        <v>16.871739130434783</v>
+        <v>16.864930729166666</v>
       </c>
       <c r="R165" s="8">
-        <v>5.0143374999999999</v>
+        <v>4.5439148148148147</v>
       </c>
       <c r="S165" s="8">
         <v>7</v>
       </c>
       <c r="T165" s="9">
-        <v>0.51449275362318836</v>
+        <v>0.5</v>
       </c>
       <c r="U165" s="9">
-        <v>0.065217391304347824</v>
+        <v>0.088541666666666671</v>
       </c>
       <c r="V165" s="9">
-        <v>0.007246376811594203</v>
+        <v>0.005208333333333333</v>
       </c>
       <c r="W165" s="9">
         <v>0</v>
       </c>
       <c r="X165" s="9">
-        <v>0.007246376811594203</v>
+        <v>0.010416666666666666</v>
       </c>
       <c r="Y165" s="9">
         <v>0</v>
       </c>
       <c r="Z165" s="9">
-        <v>0</v>
+        <v>0.015625</v>
       </c>
       <c r="AA165" s="9">
-        <v>0.043478260869565216</v>
+        <v>0.036458333333333336</v>
       </c>
       <c r="AB165" s="9">
-        <v>0.014492753623188406</v>
+        <v>0.015625</v>
       </c>
       <c r="AC165" s="9">
-        <v>0</v>
+        <v>0.010416666666666666</v>
       </c>
       <c r="AD165" s="6">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE165" s="6">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AF165" s="6">
         <v>1</v>
@@ -26272,22 +26272,22 @@
         <v>0</v>
       </c>
       <c r="AH165" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI165" s="6">
         <v>0</v>
       </c>
       <c r="AJ165" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK165" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL165" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM165" s="6">
         <v>2</v>
-      </c>
-      <c r="AM165" s="6">
-        <v>0</v>
       </c>
       <c r="AN165" s="9">
         <v>0</v>
@@ -26335,7 +26335,7 @@
         <v>19954</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C166" s="4">
         <v>51</v>
@@ -26366,31 +26366,31 @@
       </c>
       <c r="L166" s="4"/>
       <c r="M166" s="5">
-        <v>12242.801666666666</v>
+        <v>14469.01</v>
       </c>
       <c r="N166" s="6">
-        <v>135</v>
+        <v>184</v>
       </c>
       <c r="O166" s="6">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="P166" s="7">
-        <v>5.9176765151515145</v>
+        <v>7.2062613259668513</v>
       </c>
       <c r="Q166" s="8">
-        <v>16.157906410256412</v>
+        <v>16.706206382978724</v>
       </c>
       <c r="R166" s="8">
-        <v>2.6974358974358976</v>
+        <v>2.6549648936170214</v>
       </c>
       <c r="S166" s="8">
         <v>7</v>
       </c>
       <c r="T166" s="9">
-        <v>0.5</v>
+        <v>0.45744680851063829</v>
       </c>
       <c r="U166" s="9">
-        <v>0.05128205128205128</v>
+        <v>0.042553191489361701</v>
       </c>
       <c r="V166" s="9">
         <v>0</v>
@@ -26399,7 +26399,7 @@
         <v>0</v>
       </c>
       <c r="X166" s="9">
-        <v>0.01282051282051282</v>
+        <v>0.010638297872340425</v>
       </c>
       <c r="Y166" s="9">
         <v>0</v>
@@ -26411,10 +26411,10 @@
         <v>0</v>
       </c>
       <c r="AB166" s="9">
-        <v>0.01282051282051282</v>
+        <v>0.010638297872340425</v>
       </c>
       <c r="AC166" s="9">
-        <v>0.02564102564102564</v>
+        <v>0.021276595744680851</v>
       </c>
       <c r="AD166" s="6">
         <v>4</v>
@@ -26492,7 +26492,7 @@
         <v>19956</v>
       </c>
       <c r="B167" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C167" s="4">
         <v>51</v>
@@ -26523,40 +26523,40 @@
       </c>
       <c r="L167" s="4"/>
       <c r="M167" s="5">
-        <v>9706.4800000000014</v>
+        <v>11068.309999999999</v>
       </c>
       <c r="N167" s="6">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="O167" s="6">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="P167" s="7">
-        <v>6.5726086956521739</v>
+        <v>6.7416669014084505</v>
       </c>
       <c r="Q167" s="8">
-        <v>23.389284285714286</v>
+        <v>24.258927380952382</v>
       </c>
       <c r="R167" s="8">
-        <v>10.455475714285713</v>
+        <v>11.047816666666668</v>
       </c>
       <c r="S167" s="8">
         <v>7</v>
       </c>
       <c r="T167" s="9">
-        <v>0.17142857142857143</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="U167" s="9">
-        <v>0.16901408450704225</v>
+        <v>0.16470588235294117</v>
       </c>
       <c r="V167" s="9">
-        <v>0.056338028169014086</v>
+        <v>0.070588235294117646</v>
       </c>
       <c r="W167" s="9">
         <v>0</v>
       </c>
       <c r="X167" s="9">
-        <v>0.056338028169014086</v>
+        <v>0.047058823529411764</v>
       </c>
       <c r="Y167" s="9">
         <v>0</v>
@@ -26568,19 +26568,19 @@
         <v>0</v>
       </c>
       <c r="AB167" s="9">
-        <v>0.042253521126760563</v>
+        <v>0.035294117647058823</v>
       </c>
       <c r="AC167" s="9">
-        <v>0.042253521126760563</v>
+        <v>0.035294117647058823</v>
       </c>
       <c r="AD167" s="6">
+        <v>16</v>
+      </c>
+      <c r="AE167" s="6">
         <v>14</v>
       </c>
-      <c r="AE167" s="6">
-        <v>12</v>
-      </c>
       <c r="AF167" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG167" s="6">
         <v>0</v>
@@ -26963,7 +26963,7 @@
         <v>19961</v>
       </c>
       <c r="B170" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C170" s="4">
         <v>51</v>
@@ -26994,61 +26994,61 @@
       </c>
       <c r="L170" s="4"/>
       <c r="M170" s="5">
-        <v>21755.404999999999</v>
+        <v>22541.039999999997</v>
       </c>
       <c r="N170" s="6">
-        <v>204</v>
+        <v>246</v>
       </c>
       <c r="O170" s="6">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="P170" s="7">
-        <v>7.2272572916666666</v>
+        <v>6.9891056277056283</v>
       </c>
       <c r="Q170" s="8">
-        <v>24.595061111111111</v>
+        <v>23.610559541984731</v>
       </c>
       <c r="R170" s="8">
-        <v>10.261793396226414</v>
+        <v>9.5944449612403098</v>
       </c>
       <c r="S170" s="8">
         <v>7</v>
       </c>
       <c r="T170" s="9">
-        <v>0.26851851851851855</v>
+        <v>0.27480916030534353</v>
       </c>
       <c r="U170" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.15267175572519084</v>
       </c>
       <c r="V170" s="9">
-        <v>0.018518518518518517</v>
+        <v>0.015267175572519083</v>
       </c>
       <c r="W170" s="9">
         <v>0</v>
       </c>
       <c r="X170" s="9">
-        <v>0.027777777777777776</v>
+        <v>0.030534351145038167</v>
       </c>
       <c r="Y170" s="9">
-        <v>0.0092592592592592587</v>
+        <v>0.0076335877862595417</v>
       </c>
       <c r="Z170" s="9">
         <v>0</v>
       </c>
       <c r="AA170" s="9">
-        <v>0.092592592592592587</v>
+        <v>0.091603053435114504</v>
       </c>
       <c r="AB170" s="9">
         <v>0</v>
       </c>
       <c r="AC170" s="9">
-        <v>0.037037037037037035</v>
+        <v>0.030534351145038167</v>
       </c>
       <c r="AD170" s="6">
+        <v>23</v>
+      </c>
+      <c r="AE170" s="6">
         <v>20</v>
-      </c>
-      <c r="AE170" s="6">
-        <v>18</v>
       </c>
       <c r="AF170" s="6">
         <v>2</v>
@@ -27057,7 +27057,7 @@
         <v>0</v>
       </c>
       <c r="AH170" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI170" s="6">
         <v>1</v>
@@ -27066,7 +27066,7 @@
         <v>0</v>
       </c>
       <c r="AK170" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL170" s="6">
         <v>0</v>
